--- a/astro-site/public/dl/kit-plan-financiero/BONUS-09-checklist-pre-apertura.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/BONUS-09-checklist-pre-apertura.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Checklist" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checklist'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
-    <numFmt formatCode="0.0%" numFmtId="165"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -171,39 +173,39 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -563,15 +565,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="85"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -579,6 +582,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -586,6 +590,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -621,9 +626,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -673,8 +676,25 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -683,18 +703,18 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="22"/>
-    <col customWidth="1" max="3" min="3" width="45"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="15"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="30"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,6 +731,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1852,6 +1873,7 @@
       </c>
       <c r="G52" s="10" t="n"/>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="B54" s="16" t="inlineStr">
         <is>
@@ -1877,7 +1899,7 @@
       </c>
       <c r="C56" s="18">
         <f>COUNTIF(F5:F52,"Completada")</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
@@ -1888,7 +1910,7 @@
       </c>
       <c r="C57" s="18">
         <f>COUNTIF(F5:F52,"En curso")</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
@@ -1899,7 +1921,7 @@
       </c>
       <c r="C58" s="18">
         <f>COUNTIF(F5:F52,"Pendiente")</f>
-        <v/>
+        <v>48.0</v>
       </c>
     </row>
     <row r="59">
@@ -1910,9 +1932,10 @@
       </c>
       <c r="C59" s="19">
         <f>COUNTIF(F5:F52,"Completada")/48</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="20" t="inlineStr">
         <is>
@@ -1927,10 +1950,19 @@
     <mergeCell ref="A61:G61"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Selecciona: Pendiente, En curso o Completada" errorTitle="Estado no válido" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Estado no válido" error="Selecciona: Pendiente, En curso o Completada" type="list">
       <formula1>"Pendiente,En curso,Completada"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-plan-financiero/BONUS-09-checklist-pre-apertura.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/BONUS-09-checklist-pre-apertura.xlsx
@@ -19,11 +19,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,8 +99,18 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -148,6 +159,41 @@
         <bgColor rgb="00E0F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEDC8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDE7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -175,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -201,10 +247,80 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -567,18 +683,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>BONUS 09 · Checklist Financiero Pre-Apertura — 48 Tareas</t>
+          <t>BONUS 09 · Checklist Financiero Pre-Apertura — 54 Tareas</t>
         </is>
       </c>
     </row>
@@ -601,7 +717,7 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>▸ 48 tareas organizadas en 6 fases: Constitución, Financiación, Licencias, Proveedores, Seguros, Tesorería.</t>
+          <t>▸ 54 tareas organizadas en 7 fases: Constitución, Financiación, Licencias, Proveedores, Seguros, Tesorería y Personal.</t>
         </is>
       </c>
     </row>
@@ -678,13 +794,48 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+      <c r="B20" s="4" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>▸ Fase 7: Personal y obligaciones laborales (SS, RETA, apertura del centro de trabajo, contratos del convenio, altas previas, registro de jornada y modelo 111).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>▸ El «% Completado» cuenta las tareas que hay, no un número escrito a mano: si añades las tuyas hasta la fila 64, el porcentaje las incluye.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Para editar una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -705,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -720,7 +871,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Checklist Financiero Pre-Apertura — 48 Tareas</t>
+          <t>Checklist Financiero Pre-Apertura — 54 Tareas</t>
         </is>
       </c>
     </row>
@@ -773,7 +924,7 @@
       <c r="A5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>1. Constitución</t>
         </is>
@@ -783,20 +934,20 @@
           <t>Elegir forma jurídica (SL, autónomo, cooperativa)</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>1. Constitución</t>
         </is>
@@ -806,20 +957,20 @@
           <t>Escritura de constitución ante notario</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>1. Constitución</t>
         </is>
@@ -829,20 +980,20 @@
           <t>Inscripción en Registro Mercantil</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>1. Constitución</t>
         </is>
@@ -852,20 +1003,20 @@
           <t>Obtener NIF/CIF definitivo</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>1. Constitución</t>
         </is>
@@ -875,20 +1026,20 @@
           <t>Apertura de cuenta bancaria empresarial</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>1. Constitución</t>
         </is>
@@ -898,20 +1049,20 @@
           <t>Libro de actas y libro de socios</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>1. Constitución</t>
         </is>
@@ -921,20 +1072,20 @@
           <t>Alta en el Censo de Empresarios (Modelo 036/037)</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>1. Constitución</t>
         </is>
@@ -944,20 +1095,20 @@
           <t>Registro de marca / nombre comercial (OEPM)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>2. Financiación</t>
         </is>
@@ -967,20 +1118,20 @@
           <t>Elaborar plan financiero completo</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>2. Financiación</t>
         </is>
@@ -990,20 +1141,20 @@
           <t>Calcular necesidades de inversión (CAPEX)</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>2. Financiación</t>
         </is>
@@ -1013,20 +1164,20 @@
           <t>Determinar capital circulante necesario (3-6 meses)</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>2. Financiación</t>
         </is>
@@ -1036,20 +1187,20 @@
           <t>Solicitar préstamo ICO / línea de crédito</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>2. Financiación</t>
         </is>
@@ -1059,20 +1210,20 @@
           <t>Evaluar subvenciones autonómicas/locales</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>2. Financiación</t>
         </is>
@@ -1082,20 +1233,20 @@
           <t>Presentar proyecto a inversores privados</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>2. Financiación</t>
         </is>
@@ -1105,20 +1256,20 @@
           <t>Negociar condiciones bancarias (tipo, plazo, carencia)</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>2. Financiación</t>
         </is>
@@ -1128,20 +1279,20 @@
           <t>Firmar contratos de financiación</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>3. Licencias</t>
         </is>
@@ -1151,20 +1302,20 @@
           <t>Licencia de actividad / apertura</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>3. Licencias</t>
         </is>
@@ -1174,20 +1325,20 @@
           <t>Licencia de obras (si reformas)</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>3. Licencias</t>
         </is>
@@ -1197,20 +1348,20 @@
           <t>Proyecto técnico (arquitecto/ingeniero)</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>3. Licencias</t>
         </is>
@@ -1220,20 +1371,20 @@
           <t>Certificado de solidez / estructura</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>3. Licencias</t>
         </is>
@@ -1243,20 +1394,20 @@
           <t>Autorización sanitaria (Registro Sanitario)</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>3. Licencias</t>
         </is>
@@ -1266,20 +1417,20 @@
           <t>Inscripción RGSEAA (si elaboración)</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>3. Licencias</t>
         </is>
@@ -1289,20 +1440,20 @@
           <t>Plan de autoprotección (si aforo &gt; 50)</t>
         </is>
       </c>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>3. Licencias</t>
         </is>
@@ -1312,20 +1463,20 @@
           <t>Contrato de gestión de residuos</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>4. Proveedores</t>
         </is>
@@ -1335,20 +1486,20 @@
           <t>Seleccionar distribuidor principal (alimentación)</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>4. Proveedores</t>
         </is>
@@ -1358,20 +1509,20 @@
           <t>Contratar suministros (luz, agua, gas)</t>
         </is>
       </c>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>4. Proveedores</t>
         </is>
@@ -1381,20 +1532,20 @@
           <t>Negociar contrato de alquiler y fianza</t>
         </is>
       </c>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>4. Proveedores</t>
         </is>
@@ -1404,20 +1555,20 @@
           <t>Contratar servicio de lavandería</t>
         </is>
       </c>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>4. Proveedores</t>
         </is>
@@ -1427,20 +1578,20 @@
           <t>Contratar mantenimiento de equipos</t>
         </is>
       </c>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>4. Proveedores</t>
         </is>
@@ -1450,20 +1601,20 @@
           <t>Contratar servicio de desratización (DDD)</t>
         </is>
       </c>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>4. Proveedores</t>
         </is>
@@ -1473,20 +1624,20 @@
           <t>Firmar contrato con plataformas delivery</t>
         </is>
       </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>4. Proveedores</t>
         </is>
@@ -1496,20 +1647,20 @@
           <t>Negociar condiciones de pago con proveedores clave</t>
         </is>
       </c>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B37" s="29" t="inlineStr">
         <is>
           <t>5. Seguros</t>
         </is>
@@ -1519,20 +1670,20 @@
           <t>Seguro de responsabilidad civil</t>
         </is>
       </c>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="24" t="n"/>
+      <c r="F37" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>5. Seguros</t>
         </is>
@@ -1542,20 +1693,20 @@
           <t>Seguro multirriesgo del local</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="24" t="n"/>
+      <c r="F38" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B39" s="29" t="inlineStr">
         <is>
           <t>5. Seguros</t>
         </is>
@@ -1565,20 +1716,20 @@
           <t>Seguro de accidentes de trabajo</t>
         </is>
       </c>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t>5. Seguros</t>
         </is>
@@ -1588,20 +1739,20 @@
           <t>Seguro de pérdida de beneficios</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="24" t="n"/>
+      <c r="F40" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B41" s="29" t="inlineStr">
         <is>
           <t>5. Seguros</t>
         </is>
@@ -1611,20 +1762,20 @@
           <t>Seguro de mercancías (cámaras frías)</t>
         </is>
       </c>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="24" t="n"/>
+      <c r="F41" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B42" s="29" t="inlineStr">
         <is>
           <t>5. Seguros</t>
         </is>
@@ -1634,20 +1785,20 @@
           <t>Seguro de responsabilidad de administradores</t>
         </is>
       </c>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="n"/>
+      <c r="D42" s="23" t="n"/>
+      <c r="E42" s="24" t="n"/>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B43" s="29" t="inlineStr">
         <is>
           <t>5. Seguros</t>
         </is>
@@ -1657,20 +1808,20 @@
           <t>Seguro de ciberriesgos (si TPV/web)</t>
         </is>
       </c>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="24" t="n"/>
+      <c r="F43" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B44" s="29" t="inlineStr">
         <is>
           <t>5. Seguros</t>
         </is>
@@ -1680,20 +1831,20 @@
           <t>Seguro de caución (si aplica)</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="n"/>
+      <c r="D44" s="23" t="n"/>
+      <c r="E44" s="24" t="n"/>
+      <c r="F44" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>6. Tesorería</t>
         </is>
@@ -1703,20 +1854,20 @@
           <t>Configurar TPV y datáfonos</t>
         </is>
       </c>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="24" t="n"/>
+      <c r="F45" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>6. Tesorería</t>
         </is>
@@ -1726,20 +1877,20 @@
           <t>Activar pasarela de pago online</t>
         </is>
       </c>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="n"/>
+      <c r="D46" s="23" t="n"/>
+      <c r="E46" s="24" t="n"/>
+      <c r="F46" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>6. Tesorería</t>
         </is>
@@ -1749,20 +1900,20 @@
           <t>Configurar software de facturación (Veri*factu)</t>
         </is>
       </c>
-      <c r="D47" s="10" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="n"/>
+      <c r="D47" s="23" t="n"/>
+      <c r="E47" s="24" t="n"/>
+      <c r="F47" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>6. Tesorería</t>
         </is>
@@ -1772,20 +1923,20 @@
           <t>Establecer fondo de caja (efectivo inicial)</t>
         </is>
       </c>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="n"/>
+      <c r="D48" s="23" t="n"/>
+      <c r="E48" s="24" t="n"/>
+      <c r="F48" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="30" t="inlineStr">
         <is>
           <t>6. Tesorería</t>
         </is>
@@ -1795,20 +1946,20 @@
           <t>Definir política de propinas</t>
         </is>
       </c>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="n"/>
+      <c r="D49" s="23" t="n"/>
+      <c r="E49" s="24" t="n"/>
+      <c r="F49" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>6. Tesorería</t>
         </is>
@@ -1818,20 +1969,20 @@
           <t>Configurar domiciliaciones (alquiler, suministros)</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="24" t="n"/>
+      <c r="F50" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="30" t="inlineStr">
         <is>
           <t>6. Tesorería</t>
         </is>
@@ -1841,20 +1992,20 @@
           <t>Crear previsión de tesorería mes 1-3</t>
         </is>
       </c>
-      <c r="D51" s="10" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G51" s="10" t="n"/>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="24" t="n"/>
+      <c r="F51" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="30" t="inlineStr">
         <is>
           <t>6. Tesorería</t>
         </is>
@@ -1864,93 +2015,293 @@
           <t>Establecer umbral de alerta de tesorería</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="11" t="n"/>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="n"/>
-    </row>
-    <row r="53"/>
+      <c r="D52" s="23" t="n"/>
+      <c r="E52" s="24" t="n"/>
+      <c r="F52" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>7. Personal y obligaciones laborales</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Inscribir la empresa en la Seguridad Social y obtener el CCC</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="n"/>
+      <c r="E53" s="33" t="n"/>
+      <c r="F53" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G53" s="32" t="n"/>
+    </row>
     <row r="54">
-      <c r="B54" s="16" t="inlineStr">
+      <c r="A54" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="31" t="inlineStr">
+        <is>
+          <t>7. Personal y obligaciones laborales</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Alta del promotor/a en el RETA (o régimen que corresponda)</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="33" t="n"/>
+      <c r="F54" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G54" s="32" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>7. Personal y obligaciones laborales</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Comunicación de apertura del centro de trabajo a la autoridad laboral</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="n"/>
+      <c r="E55" s="33" t="n"/>
+      <c r="F55" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G55" s="32" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="31" t="inlineStr">
+        <is>
+          <t>7. Personal y obligaciones laborales</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Contratos según el convenio provincial de hostelería</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="n"/>
+      <c r="E56" s="33" t="n"/>
+      <c r="F56" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G56" s="32" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="31" t="inlineStr">
+        <is>
+          <t>7. Personal y obligaciones laborales</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Alta de los trabajadores en la SS ANTES del inicio de la jornada</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="n"/>
+      <c r="E57" s="33" t="n"/>
+      <c r="F57" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G57" s="32" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>7. Personal y obligaciones laborales</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Registro de jornada y calendario de nóminas y del modelo 111</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="n"/>
+      <c r="E58" s="33" t="n"/>
+      <c r="F58" s="25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G58" s="32" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="34" t="n"/>
+      <c r="D59" s="32" t="n"/>
+      <c r="E59" s="33" t="n"/>
+      <c r="F59" s="32" t="n"/>
+      <c r="G59" s="32" t="n"/>
+    </row>
+    <row r="60">
+      <c r="D60" s="32" t="n"/>
+      <c r="E60" s="33" t="n"/>
+      <c r="F60" s="32" t="n"/>
+      <c r="G60" s="32" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="n"/>
+      <c r="D61" s="32" t="n"/>
+      <c r="E61" s="33" t="n"/>
+      <c r="F61" s="32" t="n"/>
+      <c r="G61" s="32" t="n"/>
+    </row>
+    <row r="62">
+      <c r="D62" s="32" t="n"/>
+      <c r="E62" s="33" t="n"/>
+      <c r="F62" s="32" t="n"/>
+      <c r="G62" s="32" t="n"/>
+    </row>
+    <row r="63">
+      <c r="D63" s="32" t="n"/>
+      <c r="E63" s="33" t="n"/>
+      <c r="F63" s="32" t="n"/>
+      <c r="G63" s="32" t="n"/>
+    </row>
+    <row r="64">
+      <c r="D64" s="32" t="n"/>
+      <c r="E64" s="33" t="n"/>
+      <c r="F64" s="32" t="n"/>
+      <c r="G64" s="32" t="n"/>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="B66" s="35" t="inlineStr">
         <is>
           <t>RESUMEN</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="17" t="inlineStr">
+    <row r="67">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Total tareas:</t>
         </is>
       </c>
-      <c r="C55" s="17" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="17" t="inlineStr">
+      <c r="C67" s="36">
+        <f>COUNTIF($A$5:$A$64,"&lt;&gt;")</f>
+        <v>54.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Completadas:</t>
         </is>
       </c>
-      <c r="C56" s="18">
-        <f>COUNTIF(F5:F52,"Completada")</f>
+      <c r="C68" s="36">
+        <f>COUNTIF($F$5:$F$64,"Completada")</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="17" t="inlineStr">
+    <row r="69">
+      <c r="B69" t="inlineStr">
         <is>
           <t>En curso:</t>
         </is>
       </c>
-      <c r="C57" s="18">
-        <f>COUNTIF(F5:F52,"En curso")</f>
+      <c r="C69" s="36">
+        <f>COUNTIF($F$5:$F$64,"En curso")</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="17" t="inlineStr">
+    <row r="70">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Pendientes:</t>
         </is>
       </c>
-      <c r="C58" s="18">
-        <f>COUNTIF(F5:F52,"Pendiente")</f>
-        <v>48.0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="17" t="inlineStr">
+      <c r="C70" s="36">
+        <f>COUNTIF($F$5:$F$64,"Pendiente")</f>
+        <v>54.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
         <is>
           <t>% Completado:</t>
         </is>
       </c>
-      <c r="C59" s="19">
-        <f>COUNTIF(F5:F52,"Completada")/48</f>
+      <c r="C71" s="37">
+        <f>IFERROR(COUNTIF($F$5:$F$64,"Completada")/$C$67,0)</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+    <row r="72"/>
+    <row r="73">
+      <c r="B73" s="38" t="inlineStr">
+        <is>
+          <t>El total se CUENTA, no se escribe: si añades tareas tuyas en las filas libres (hasta la 64), el porcentaje sigue siendo cierto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="39" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
   </sheetData>
-  <mergeCells count="3">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A61:G61"/>
   </mergeCells>
+  <conditionalFormatting sqref="F5:F64">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" stopIfTrue="1" text="Completada">
+      <formula>NOT(ISERROR(SEARCH("Completada",F5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="En curso">
+      <formula>NOT(ISERROR(SEARCH("En curso",F5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" stopIfTrue="1" text="Pendiente">
+      <formula>NOT(ISERROR(SEARCH("Pendiente",F5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Estado no válido" error="Selecciona: Pendiente, En curso o Completada" type="list">
+    <dataValidation sqref="F5:F64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estado no válido" error="Elige Pendiente, En curso o Completada." type="list">
       <formula1>"Pendiente,En curso,Completada"</formula1>
     </dataValidation>
   </dataValidations>
